--- a/Ozrit HR data/ozrit/HR/Employee Details/Employee Data/Employees data.xlsx
+++ b/Ozrit HR data/ozrit/HR/Employee Details/Employee Data/Employees data.xlsx
@@ -8,13 +8,18 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Rani\Downloads\ozrit\Ozrit HR data\ozrit\HR\Employee Details\Employee Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{004AB565-9AD1-4699-90E0-077F36828094}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78881FFB-851D-4151-8611-9A92EAA2A0AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
+    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Sheet2!$A$1:$K$54</definedName>
+  </definedNames>
   <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -25,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="219" uniqueCount="197">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="480" uniqueCount="336">
   <si>
     <t>EMP Code</t>
   </si>
@@ -616,6 +621,423 @@
   </si>
   <si>
     <t>14.09.2023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SL no </t>
+  </si>
+  <si>
+    <t>Employee ID</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Name </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Department </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Role </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rani kumari </t>
+  </si>
+  <si>
+    <t xml:space="preserve">HR </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nisa Touseef </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recruiter </t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mahesh </t>
+  </si>
+  <si>
+    <t xml:space="preserve">CRE </t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jaya kumari </t>
+  </si>
+  <si>
+    <t xml:space="preserve">wordpress developer </t>
+  </si>
+  <si>
+    <t xml:space="preserve">050 </t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Asif </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Project Manager </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kumar </t>
+  </si>
+  <si>
+    <t>Full stack developer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sanjay </t>
+  </si>
+  <si>
+    <t xml:space="preserve">PHP trainee </t>
+  </si>
+  <si>
+    <t xml:space="preserve">wordpress </t>
+  </si>
+  <si>
+    <t>PHP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vishwa </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mobile application </t>
+  </si>
+  <si>
+    <t>Varun</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Flutter develper </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sai charan </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Anvesh </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Node js </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mernstack developer </t>
+  </si>
+  <si>
+    <t>Veeresh</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nodejs </t>
+  </si>
+  <si>
+    <t>Intern</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Harshith </t>
+  </si>
+  <si>
+    <t>Trainee</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Surya </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Designer </t>
+  </si>
+  <si>
+    <t>UI?UX</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Manikanta </t>
+  </si>
+  <si>
+    <t>Ui/ux Trainee</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Abhinay </t>
+  </si>
+  <si>
+    <t>Graphic Trainee</t>
+  </si>
+  <si>
+    <t>Interm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chetan </t>
+  </si>
+  <si>
+    <t>QA</t>
+  </si>
+  <si>
+    <t>Sayeed</t>
+  </si>
+  <si>
+    <t>Cloud associate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raghu </t>
+  </si>
+  <si>
+    <t xml:space="preserve">DM </t>
+  </si>
+  <si>
+    <t xml:space="preserve">DM Lead </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chari </t>
+  </si>
+  <si>
+    <t>DM Associate</t>
+  </si>
+  <si>
+    <t>Sanajana</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yuvraj </t>
+  </si>
+  <si>
+    <t>Kiran</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Neelesh </t>
+  </si>
+  <si>
+    <t>sireesha</t>
+  </si>
+  <si>
+    <t>Sharan</t>
+  </si>
+  <si>
+    <t>Venkatesh</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vamshi </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vamshi krishna </t>
+  </si>
+  <si>
+    <t>Narsimha</t>
+  </si>
+  <si>
+    <t>Anuroop</t>
+  </si>
+  <si>
+    <t>Mohan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Phani </t>
+  </si>
+  <si>
+    <t>Sales</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sales lead </t>
+  </si>
+  <si>
+    <t>Ravindr</t>
+  </si>
+  <si>
+    <t>sales</t>
+  </si>
+  <si>
+    <t>BDE</t>
+  </si>
+  <si>
+    <t>Manish</t>
+  </si>
+  <si>
+    <t>Harika</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dinesh </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python </t>
+  </si>
+  <si>
+    <t>Python POC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Balaji </t>
+  </si>
+  <si>
+    <t>Nasaraiah</t>
+  </si>
+  <si>
+    <t>Python jr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nani </t>
+  </si>
+  <si>
+    <t xml:space="preserve">jr. developer </t>
+  </si>
+  <si>
+    <t xml:space="preserve">siri teja </t>
+  </si>
+  <si>
+    <t>jr.developer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pavan </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pradeep </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lakshman </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Angular </t>
+  </si>
+  <si>
+    <t>Angular</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gopi </t>
+  </si>
+  <si>
+    <t>React</t>
+  </si>
+  <si>
+    <t>Sr. POC</t>
+  </si>
+  <si>
+    <t>Yuva kiran</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hruthik </t>
+  </si>
+  <si>
+    <t xml:space="preserve">SR. developer </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Niharika </t>
+  </si>
+  <si>
+    <t>Hema</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pranitha </t>
+  </si>
+  <si>
+    <t>vijay</t>
+  </si>
+  <si>
+    <t>swamy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">wordpress  POC </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Designer POC </t>
+  </si>
+  <si>
+    <t>Mobile application poc</t>
+  </si>
+  <si>
+    <t>DM Poc</t>
+  </si>
+  <si>
+    <t>Sales POC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">React poc </t>
+  </si>
+  <si>
+    <t>Python poc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Experience </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Appointment </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Policy </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Agreement </t>
+  </si>
+  <si>
+    <t>Onboarding proess /document Collection</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BGV </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Done </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Not done </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Internship </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ads </t>
+  </si>
+  <si>
+    <t xml:space="preserve">chari , </t>
+  </si>
+  <si>
+    <t xml:space="preserve">raghu </t>
+  </si>
+  <si>
+    <t xml:space="preserve">mohan </t>
+  </si>
+  <si>
+    <t xml:space="preserve">kiran </t>
+  </si>
+  <si>
+    <t>sanjana</t>
+  </si>
+  <si>
+    <t xml:space="preserve">meghana </t>
+  </si>
+  <si>
+    <t xml:space="preserve">client handling </t>
+  </si>
+  <si>
+    <t xml:space="preserve">posting </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ozrit </t>
+  </si>
+  <si>
+    <t xml:space="preserve">team </t>
+  </si>
+  <si>
+    <t>sharan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">yuv </t>
+  </si>
+  <si>
+    <t xml:space="preserve">neelesh </t>
+  </si>
+  <si>
+    <t xml:space="preserve">chari </t>
+  </si>
+  <si>
+    <t xml:space="preserve">night shift </t>
+  </si>
+  <si>
+    <t xml:space="preserve">blog </t>
+  </si>
+  <si>
+    <t xml:space="preserve">everything , seo except designing </t>
+  </si>
+  <si>
+    <t xml:space="preserve">narasimha </t>
+  </si>
+  <si>
+    <t xml:space="preserve">vamshi </t>
+  </si>
+  <si>
+    <t xml:space="preserve">scheduling ,seo , backlinks </t>
   </si>
 </sst>
 </file>
@@ -713,7 +1135,7 @@
       <family val="1"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -724,6 +1146,36 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
         <bgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -807,7 +1259,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="60">
+  <cellXfs count="72">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -986,6 +1438,18 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -11818,4 +12282,1026 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId35"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C7D8F0E-7E6C-4B19-A5F4-BBBC237BF79E}">
+  <sheetPr filterMode="1"/>
+  <dimension ref="A1:K1048576"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="8.7265625" style="60"/>
+    <col min="2" max="2" width="11.26953125" style="60" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.6328125" customWidth="1"/>
+    <col min="4" max="4" width="19.90625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="19.08984375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.36328125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="35.6328125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.26953125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="6" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.6328125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A1" s="60" t="s">
+        <v>197</v>
+      </c>
+      <c r="B1" s="60" t="s">
+        <v>198</v>
+      </c>
+      <c r="C1" t="s">
+        <v>199</v>
+      </c>
+      <c r="D1" t="s">
+        <v>200</v>
+      </c>
+      <c r="E1" t="s">
+        <v>201</v>
+      </c>
+      <c r="F1" t="s">
+        <v>306</v>
+      </c>
+      <c r="G1" t="s">
+        <v>310</v>
+      </c>
+      <c r="H1" t="s">
+        <v>307</v>
+      </c>
+      <c r="I1" t="s">
+        <v>308</v>
+      </c>
+      <c r="J1" t="s">
+        <v>309</v>
+      </c>
+      <c r="K1" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="60">
+        <v>1</v>
+      </c>
+      <c r="B2" s="60" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" t="s">
+        <v>202</v>
+      </c>
+      <c r="D2" t="s">
+        <v>203</v>
+      </c>
+      <c r="E2" t="s">
+        <v>203</v>
+      </c>
+      <c r="G2" s="61" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="60" t="s">
+        <v>204</v>
+      </c>
+      <c r="C3" t="s">
+        <v>205</v>
+      </c>
+      <c r="D3" t="s">
+        <v>203</v>
+      </c>
+      <c r="E3" t="s">
+        <v>206</v>
+      </c>
+      <c r="G3" s="61" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="60" t="s">
+        <v>207</v>
+      </c>
+      <c r="B4" s="60" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4" t="s">
+        <v>208</v>
+      </c>
+      <c r="D4" t="s">
+        <v>299</v>
+      </c>
+      <c r="E4" t="s">
+        <v>209</v>
+      </c>
+      <c r="G4" s="61" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="60" t="s">
+        <v>210</v>
+      </c>
+      <c r="B5" s="60" t="s">
+        <v>213</v>
+      </c>
+      <c r="C5" t="s">
+        <v>211</v>
+      </c>
+      <c r="D5" t="s">
+        <v>221</v>
+      </c>
+      <c r="E5" t="s">
+        <v>212</v>
+      </c>
+      <c r="G5" s="61" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="60" t="s">
+        <v>214</v>
+      </c>
+      <c r="B6" s="60" t="s">
+        <v>15</v>
+      </c>
+      <c r="C6" t="s">
+        <v>215</v>
+      </c>
+      <c r="D6" t="s">
+        <v>222</v>
+      </c>
+      <c r="E6" t="s">
+        <v>216</v>
+      </c>
+      <c r="G6" s="61" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+      <c r="C7" t="s">
+        <v>217</v>
+      </c>
+      <c r="D7" t="s">
+        <v>222</v>
+      </c>
+      <c r="E7" t="s">
+        <v>218</v>
+      </c>
+      <c r="G7" s="61" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+      <c r="C8" t="s">
+        <v>219</v>
+      </c>
+      <c r="D8" t="s">
+        <v>222</v>
+      </c>
+      <c r="E8" t="s">
+        <v>220</v>
+      </c>
+      <c r="G8" s="61" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+      <c r="C9" t="s">
+        <v>223</v>
+      </c>
+      <c r="D9" t="s">
+        <v>301</v>
+      </c>
+      <c r="E9" t="s">
+        <v>55</v>
+      </c>
+      <c r="G9" s="61" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+      <c r="C10" t="s">
+        <v>225</v>
+      </c>
+      <c r="D10" t="s">
+        <v>301</v>
+      </c>
+      <c r="E10" t="s">
+        <v>226</v>
+      </c>
+      <c r="G10" s="61" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+      <c r="C11" t="s">
+        <v>227</v>
+      </c>
+      <c r="D11" t="s">
+        <v>224</v>
+      </c>
+      <c r="E11" t="s">
+        <v>226</v>
+      </c>
+      <c r="G11" s="61" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+      <c r="C12" t="s">
+        <v>228</v>
+      </c>
+      <c r="D12" t="s">
+        <v>229</v>
+      </c>
+      <c r="E12" t="s">
+        <v>230</v>
+      </c>
+      <c r="G12" s="71" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A13" s="60" t="s">
+        <v>233</v>
+      </c>
+      <c r="C13" t="s">
+        <v>231</v>
+      </c>
+      <c r="D13" t="s">
+        <v>229</v>
+      </c>
+      <c r="E13" t="s">
+        <v>232</v>
+      </c>
+      <c r="G13" s="63" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A14" s="60" t="s">
+        <v>233</v>
+      </c>
+      <c r="C14" t="s">
+        <v>234</v>
+      </c>
+      <c r="D14" t="s">
+        <v>229</v>
+      </c>
+      <c r="E14" t="s">
+        <v>235</v>
+      </c>
+      <c r="G14" s="63" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+      <c r="C15" t="s">
+        <v>236</v>
+      </c>
+      <c r="D15" t="s">
+        <v>300</v>
+      </c>
+      <c r="E15" t="s">
+        <v>238</v>
+      </c>
+      <c r="G15" s="62" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A16" s="60" t="s">
+        <v>243</v>
+      </c>
+      <c r="C16" t="s">
+        <v>239</v>
+      </c>
+      <c r="D16" t="s">
+        <v>237</v>
+      </c>
+      <c r="E16" t="s">
+        <v>240</v>
+      </c>
+      <c r="G16" s="63" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A17" s="60" t="s">
+        <v>243</v>
+      </c>
+      <c r="C17" t="s">
+        <v>241</v>
+      </c>
+      <c r="D17" t="s">
+        <v>237</v>
+      </c>
+      <c r="E17" t="s">
+        <v>242</v>
+      </c>
+      <c r="G17" s="63" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="C18" t="s">
+        <v>244</v>
+      </c>
+      <c r="D18" t="s">
+        <v>245</v>
+      </c>
+      <c r="E18" t="s">
+        <v>245</v>
+      </c>
+      <c r="G18" s="62" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="C19" t="s">
+        <v>246</v>
+      </c>
+      <c r="D19" t="s">
+        <v>247</v>
+      </c>
+      <c r="E19" t="s">
+        <v>247</v>
+      </c>
+      <c r="G19" s="61" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="C20" t="s">
+        <v>248</v>
+      </c>
+      <c r="D20" t="s">
+        <v>302</v>
+      </c>
+      <c r="E20" t="s">
+        <v>250</v>
+      </c>
+      <c r="G20" s="62" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="C21" t="s">
+        <v>251</v>
+      </c>
+      <c r="D21" t="s">
+        <v>249</v>
+      </c>
+      <c r="E21" t="s">
+        <v>252</v>
+      </c>
+      <c r="G21" s="61" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="C22" t="s">
+        <v>253</v>
+      </c>
+      <c r="D22" t="s">
+        <v>249</v>
+      </c>
+      <c r="E22" t="s">
+        <v>252</v>
+      </c>
+      <c r="G22" s="62" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="C23" t="s">
+        <v>254</v>
+      </c>
+      <c r="D23" t="s">
+        <v>249</v>
+      </c>
+      <c r="E23" t="s">
+        <v>235</v>
+      </c>
+      <c r="G23" s="63" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="C24" t="s">
+        <v>255</v>
+      </c>
+      <c r="D24" t="s">
+        <v>249</v>
+      </c>
+      <c r="E24" t="s">
+        <v>235</v>
+      </c>
+      <c r="G24" s="63" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="C25" t="s">
+        <v>256</v>
+      </c>
+      <c r="D25" t="s">
+        <v>249</v>
+      </c>
+      <c r="E25" t="s">
+        <v>235</v>
+      </c>
+      <c r="G25" s="63" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="C26" t="s">
+        <v>257</v>
+      </c>
+      <c r="D26" t="s">
+        <v>249</v>
+      </c>
+      <c r="E26" t="s">
+        <v>235</v>
+      </c>
+      <c r="G26" s="63" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="C27" t="s">
+        <v>258</v>
+      </c>
+      <c r="D27" t="s">
+        <v>249</v>
+      </c>
+      <c r="E27" t="s">
+        <v>235</v>
+      </c>
+      <c r="G27" s="63" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="C28" t="s">
+        <v>259</v>
+      </c>
+      <c r="D28" t="s">
+        <v>249</v>
+      </c>
+      <c r="E28" t="s">
+        <v>235</v>
+      </c>
+      <c r="G28" s="63" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="C29" t="s">
+        <v>260</v>
+      </c>
+      <c r="D29" t="s">
+        <v>249</v>
+      </c>
+      <c r="E29" t="s">
+        <v>235</v>
+      </c>
+      <c r="G29" s="63" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="C30" t="s">
+        <v>261</v>
+      </c>
+      <c r="D30" t="s">
+        <v>249</v>
+      </c>
+      <c r="E30" t="s">
+        <v>235</v>
+      </c>
+      <c r="G30" s="63" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="C31" t="s">
+        <v>248</v>
+      </c>
+      <c r="D31" t="s">
+        <v>249</v>
+      </c>
+      <c r="E31" t="s">
+        <v>235</v>
+      </c>
+      <c r="G31" s="63" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="C32" t="s">
+        <v>262</v>
+      </c>
+      <c r="D32" t="s">
+        <v>249</v>
+      </c>
+      <c r="E32" t="s">
+        <v>235</v>
+      </c>
+      <c r="G32" s="63" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="33" spans="3:7" x14ac:dyDescent="0.35">
+      <c r="C33" t="s">
+        <v>263</v>
+      </c>
+      <c r="D33" t="s">
+        <v>249</v>
+      </c>
+      <c r="E33" t="s">
+        <v>235</v>
+      </c>
+      <c r="G33" s="63" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="34" spans="3:7" x14ac:dyDescent="0.35">
+      <c r="C34" t="s">
+        <v>264</v>
+      </c>
+      <c r="D34" t="s">
+        <v>249</v>
+      </c>
+      <c r="E34" t="s">
+        <v>235</v>
+      </c>
+      <c r="G34" s="63" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="35" spans="3:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="C35" t="s">
+        <v>265</v>
+      </c>
+      <c r="D35" t="s">
+        <v>303</v>
+      </c>
+      <c r="E35" t="s">
+        <v>267</v>
+      </c>
+      <c r="G35" s="62" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="36" spans="3:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="C36" t="s">
+        <v>268</v>
+      </c>
+      <c r="D36" t="s">
+        <v>269</v>
+      </c>
+      <c r="E36" t="s">
+        <v>270</v>
+      </c>
+      <c r="G36" s="61" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="37" spans="3:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="C37" t="s">
+        <v>271</v>
+      </c>
+      <c r="D37" t="s">
+        <v>266</v>
+      </c>
+      <c r="E37" t="s">
+        <v>270</v>
+      </c>
+      <c r="G37" s="61" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="38" spans="3:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="C38" t="s">
+        <v>272</v>
+      </c>
+      <c r="D38" t="s">
+        <v>266</v>
+      </c>
+      <c r="E38" t="s">
+        <v>270</v>
+      </c>
+      <c r="G38" s="61" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="39" spans="3:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="C39" t="s">
+        <v>273</v>
+      </c>
+      <c r="D39" t="s">
+        <v>305</v>
+      </c>
+      <c r="E39" t="s">
+        <v>275</v>
+      </c>
+      <c r="G39" s="61" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="40" spans="3:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="C40" t="s">
+        <v>276</v>
+      </c>
+      <c r="D40" t="s">
+        <v>305</v>
+      </c>
+      <c r="E40" t="s">
+        <v>275</v>
+      </c>
+      <c r="G40" s="61" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="41" spans="3:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="C41" t="s">
+        <v>277</v>
+      </c>
+      <c r="D41" t="s">
+        <v>274</v>
+      </c>
+      <c r="E41" t="s">
+        <v>278</v>
+      </c>
+      <c r="G41" s="61" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="42" spans="3:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="C42" t="s">
+        <v>279</v>
+      </c>
+      <c r="D42" t="s">
+        <v>274</v>
+      </c>
+      <c r="E42" t="s">
+        <v>280</v>
+      </c>
+      <c r="G42" s="61" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="43" spans="3:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="C43" t="s">
+        <v>281</v>
+      </c>
+      <c r="D43" t="s">
+        <v>274</v>
+      </c>
+      <c r="E43" t="s">
+        <v>282</v>
+      </c>
+      <c r="G43" s="61" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="44" spans="3:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="C44" t="s">
+        <v>283</v>
+      </c>
+      <c r="D44" t="s">
+        <v>274</v>
+      </c>
+      <c r="E44" t="s">
+        <v>282</v>
+      </c>
+      <c r="G44" s="61" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="45" spans="3:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="C45" t="s">
+        <v>284</v>
+      </c>
+      <c r="D45" t="s">
+        <v>274</v>
+      </c>
+      <c r="E45" t="s">
+        <v>235</v>
+      </c>
+      <c r="G45" s="61" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="46" spans="3:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="C46" t="s">
+        <v>285</v>
+      </c>
+      <c r="D46" t="s">
+        <v>286</v>
+      </c>
+      <c r="E46" t="s">
+        <v>287</v>
+      </c>
+      <c r="G46" s="62" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="47" spans="3:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="C47" t="s">
+        <v>288</v>
+      </c>
+      <c r="D47" t="s">
+        <v>304</v>
+      </c>
+      <c r="E47" t="s">
+        <v>290</v>
+      </c>
+      <c r="G47" s="61" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="48" spans="3:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="C48" t="s">
+        <v>291</v>
+      </c>
+      <c r="D48" t="s">
+        <v>304</v>
+      </c>
+      <c r="E48" t="s">
+        <v>290</v>
+      </c>
+      <c r="G48" s="61" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="49" spans="3:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="C49" t="s">
+        <v>292</v>
+      </c>
+      <c r="D49" t="s">
+        <v>289</v>
+      </c>
+      <c r="E49" t="s">
+        <v>293</v>
+      </c>
+      <c r="G49" s="61" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="50" spans="3:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="C50" t="s">
+        <v>294</v>
+      </c>
+      <c r="D50" t="s">
+        <v>289</v>
+      </c>
+      <c r="E50" t="s">
+        <v>282</v>
+      </c>
+      <c r="G50" s="61" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="51" spans="3:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="C51" t="s">
+        <v>295</v>
+      </c>
+      <c r="D51" t="s">
+        <v>289</v>
+      </c>
+      <c r="E51" t="s">
+        <v>282</v>
+      </c>
+      <c r="G51" s="61" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="52" spans="3:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="C52" t="s">
+        <v>296</v>
+      </c>
+      <c r="D52" t="s">
+        <v>289</v>
+      </c>
+      <c r="E52" t="s">
+        <v>282</v>
+      </c>
+      <c r="G52" s="61" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="53" spans="3:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="C53" t="s">
+        <v>297</v>
+      </c>
+      <c r="D53" t="s">
+        <v>289</v>
+      </c>
+      <c r="E53" t="s">
+        <v>282</v>
+      </c>
+      <c r="G53" s="61" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="54" spans="3:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="C54" t="s">
+        <v>298</v>
+      </c>
+      <c r="D54" t="s">
+        <v>289</v>
+      </c>
+      <c r="E54" t="s">
+        <v>282</v>
+      </c>
+      <c r="G54" s="61" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="1048576" spans="7:7" x14ac:dyDescent="0.35">
+      <c r="G1048576" s="61" t="s">
+        <v>312</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:K54" xr:uid="{3C7D8F0E-7E6C-4B19-A5F4-BBBC237BF79E}">
+    <filterColumn colId="6">
+      <filters>
+        <filter val="Internship"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3ECA4EA-29C9-4194-9551-49701A805D8C}">
+  <dimension ref="C2:E23"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="3" max="3" width="13.453125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.81640625" customWidth="1"/>
+    <col min="5" max="5" width="28.81640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C2" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="3" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C3" s="65" t="s">
+        <v>315</v>
+      </c>
+      <c r="D3" s="65" t="s">
+        <v>316</v>
+      </c>
+      <c r="E3" s="65" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="4" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C4" s="66"/>
+      <c r="D4" s="69" t="s">
+        <v>317</v>
+      </c>
+      <c r="E4" s="67" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="5" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C5" s="66"/>
+      <c r="D5" s="69" t="s">
+        <v>318</v>
+      </c>
+      <c r="E5" s="67"/>
+    </row>
+    <row r="6" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C6" s="66"/>
+      <c r="D6" s="69" t="s">
+        <v>319</v>
+      </c>
+      <c r="E6" s="67"/>
+    </row>
+    <row r="7" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C7" s="66"/>
+      <c r="D7" s="69" t="s">
+        <v>320</v>
+      </c>
+      <c r="E7" s="67"/>
+    </row>
+    <row r="8" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C8" s="66"/>
+      <c r="D8" s="69" t="s">
+        <v>321</v>
+      </c>
+      <c r="E8" s="67"/>
+    </row>
+    <row r="9" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C9" s="67"/>
+      <c r="D9" s="69"/>
+      <c r="E9" s="67"/>
+    </row>
+    <row r="10" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C10" s="65" t="s">
+        <v>324</v>
+      </c>
+      <c r="D10" s="65" t="s">
+        <v>325</v>
+      </c>
+      <c r="E10" s="65"/>
+    </row>
+    <row r="11" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C11" s="67"/>
+      <c r="D11" s="70" t="s">
+        <v>326</v>
+      </c>
+      <c r="E11" s="67" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="12" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C12" s="67"/>
+      <c r="D12" s="70" t="s">
+        <v>327</v>
+      </c>
+      <c r="E12" s="67" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="13" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C13" s="67"/>
+      <c r="D13" s="70" t="s">
+        <v>328</v>
+      </c>
+      <c r="E13" s="67"/>
+    </row>
+    <row r="14" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C14" s="67"/>
+      <c r="D14" s="70" t="s">
+        <v>257</v>
+      </c>
+      <c r="E14" s="67"/>
+    </row>
+    <row r="15" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C15" s="67"/>
+      <c r="D15" s="70" t="s">
+        <v>329</v>
+      </c>
+      <c r="E15" s="67"/>
+    </row>
+    <row r="16" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C16" s="67"/>
+      <c r="D16" s="70"/>
+      <c r="E16" s="67"/>
+    </row>
+    <row r="17" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C17" s="65" t="s">
+        <v>330</v>
+      </c>
+      <c r="D17" s="65" t="s">
+        <v>325</v>
+      </c>
+      <c r="E17" s="65"/>
+    </row>
+    <row r="18" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C18" s="67"/>
+      <c r="D18" s="68" t="s">
+        <v>317</v>
+      </c>
+      <c r="E18" s="67" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="19" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C19" s="67"/>
+      <c r="D19" s="68" t="s">
+        <v>333</v>
+      </c>
+      <c r="E19" s="67"/>
+    </row>
+    <row r="20" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C20" s="67"/>
+      <c r="D20" s="68" t="s">
+        <v>334</v>
+      </c>
+      <c r="E20" s="67"/>
+    </row>
+    <row r="21" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C21" s="67"/>
+      <c r="D21" s="68"/>
+      <c r="E21" s="67"/>
+    </row>
+    <row r="22" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C22" s="67"/>
+      <c r="D22" s="68"/>
+      <c r="E22" s="67"/>
+    </row>
+    <row r="23" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="D23" s="64"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>